--- a/app/src/main/resources/static/dre_modelo.xlsx
+++ b/app/src/main/resources/static/dre_modelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jesse\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3736E7EE-DE81-4500-935F-7A24F8C07B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F13E4B9-CBD5-4A3D-BDF9-DA1DABE33923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1811,22 +1811,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:colOff>81644</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>802821</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>445</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>299358</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>219502</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Imagem 4">
+        <xdr:cNvPr id="2" name="Imagem 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8860A169-7A9F-B630-6D32-7E7D5354E69F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39A75AA8-81C1-A5EF-2A42-5146CB7C83EB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1842,8 +1842,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="76200" y="3594100"/>
-          <a:ext cx="10590658" cy="4584700"/>
+          <a:off x="81644" y="3469821"/>
+          <a:ext cx="9593035" cy="4383288"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1855,22 +1855,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>108857</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>231321</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>753344</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:colOff>715735</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>247036</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Imagem 5">
+        <xdr:cNvPr id="9" name="Imagem 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50795EF3-8D37-22B1-4E21-5E4B51DBED34}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C37A8543-5008-E8D7-9AE4-B2279BABDCFE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1886,8 +1886,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="114300" y="8978900"/>
-          <a:ext cx="10595844" cy="5372100"/>
+          <a:off x="108857" y="9429750"/>
+          <a:ext cx="9261021" cy="4914286"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1899,22 +1899,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>139700</xdr:colOff>
+      <xdr:colOff>87087</xdr:colOff>
       <xdr:row>53</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:rowOff>27213</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>1865</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>707573</xdr:colOff>
       <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>208417</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Imagem 6">
+        <xdr:cNvPr id="10" name="Imagem 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54828CFB-4964-145D-85BC-67ADF1AB760C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F0622A1-E42C-9288-0052-04363010523D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1930,8 +1930,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="139700" y="17830800"/>
-          <a:ext cx="10573494" cy="4089400"/>
+          <a:off x="87087" y="19131642"/>
+          <a:ext cx="13601700" cy="4535489"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
